--- a/sources/eddy_step7.xlsx
+++ b/sources/eddy_step7.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA186"/>
+  <dimension ref="A1:AB186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="123" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>d4be6035-9fd4-49f2-8038-2df413319749</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>98ad5998-5629-4b2f-8dec-19d3e188ad3c</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>518c7a37-c51c-4848-b5a7-a36d35f2ee8b</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>9fae320b-20ca-449b-a554-056f4fb5f955</t>
         </is>
@@ -783,12 +789,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>3a5dc714-5027-47b2-9004-e6a50c9142bc</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>875175f3-fbb2-417c-8616-9462bdc93952</t>
         </is>
@@ -797,27 +803,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1+3 [~5]</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1+3 [~5]</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2+4 [~5]; 2+5 [~5]</t>
+          <t>2+4; 2+5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Missile Launcher [Tag]</t>
+          <t>Missile Launcher</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Missile Launcher [Tag]</t>
+          <t>Missile Launcher</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -845,12 +851,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -907,12 +918,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -969,12 +980,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>89b9a62a-0e17-41f7-9bcd-95c83f81b48a</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1106,20 +1117,25 @@
       </c>
       <c r="X11" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y11" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y11" s="1" t="inlineStr">
+      <c r="Z11" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z11" s="1" t="inlineStr">
+      <c r="AA11" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA11" s="1" t="inlineStr">
+      <c r="AB11" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1201,12 +1217,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>7cde4eba-dcb7-4864-b73a-d075c8934e96</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>6e298c50-2096-4bd3-a241-3b3d4f09e011</t>
         </is>
@@ -1288,12 +1304,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>a6933b74-2d1c-4a97-a134-6f1d77dac6c0</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>3c8b6af7-744b-4bf3-a716-54c07cb17460</t>
         </is>
@@ -1375,12 +1391,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>dfd8db19-b9a1-477a-91ca-960fb52537b0</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>2a18dda0-6de9-432b-adce-8a8375cc024d</t>
         </is>
@@ -1462,12 +1478,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>c767bf55-17af-41e7-a245-2cfbee5113e6</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>28e15c3e-4031-4742-ace3-ed8e0719c115</t>
         </is>
@@ -1549,12 +1565,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>b279de98-4a02-4d1d-874e-4f154fe3b2a5</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>909b0f04-6d0a-48ec-aa54-83d368e5d9bb</t>
         </is>
@@ -1636,12 +1652,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>57461d86-707a-4ad4-8992-d75f865b281f</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>aa8da3e2-fbbc-4c91-be1c-94d7e4d073f1</t>
         </is>
@@ -1723,12 +1739,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>5bd7cf5f-818b-4beb-87c1-c559f1118b01</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>9b0840b6-557d-45b3-b002-df304401acf6</t>
         </is>
@@ -1810,12 +1826,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>a0e50a18-48d1-4790-b09d-85604280f544</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>65e77590-11fa-420c-a811-6e34fb1f9bda</t>
         </is>
@@ -1897,12 +1913,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>0f35d092-5d92-46ed-94ce-89252be9e848</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>191c0dce-ca7a-4e2a-994b-a670d5a0997c</t>
         </is>
@@ -1984,12 +2000,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>f2b5ccb7-184e-4bcb-b11b-05712242e2df</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>b8f073c2-fbc2-4cb9-aba7-1029bbf7562c</t>
         </is>
@@ -2071,12 +2087,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>a13482a8-87f4-4a85-b77e-2ae2c0f16f47</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>9dce7ecf-e31f-4e3e-b2aa-390e60d9c4a3</t>
         </is>
@@ -2158,12 +2174,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>b46492fe-7758-4103-ad5b-0eaf65d6f121</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>a6ec6be6-40c6-4ba5-981f-fe43c93d4d03</t>
         </is>
@@ -2245,12 +2261,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>0a323682-87e6-4474-810e-84bf265e2e57</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>e402e278-9f3f-4c7f-bfd8-26c219df1e95</t>
         </is>
@@ -2332,12 +2348,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>ca3b64da-0190-4a8d-8b78-114de72ffd2a</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>09320f6e-831e-4a71-8d8f-b4140f8e8e57</t>
         </is>
@@ -2419,12 +2435,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>3a0f99cf-ce14-4d94-bb5b-6b6155e7e999</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>ce1d2c81-9d86-4639-aa1a-2ff08c643441</t>
         </is>
@@ -2506,12 +2522,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>f22ee806-86ea-4be1-b91b-0fc5d720a1a8</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>e654408a-fcc5-4429-9aa0-edd00b19ca58</t>
         </is>
@@ -2593,12 +2609,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>05a0388e-0d0b-4318-93c6-ccf976acd032</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>5156408b-a46c-4f7f-a6b0-02484dc14c44</t>
         </is>
@@ -2680,12 +2696,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>136187bc-d073-4482-93ed-275dc978e211</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>3c39f7cf-9558-4cfa-8fb7-17d1532dee65</t>
         </is>
@@ -2767,12 +2783,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>7baac16f-24fd-4794-8a47-d835f3dfccb5</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>1e78fc42-f396-4e24-8a2f-8f0457e5cdf1</t>
         </is>
@@ -2854,12 +2870,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>cb18059d-fb34-4534-ac46-173e634658fe</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>bcba6134-aac3-4cb0-afb1-062d8e7d3291</t>
         </is>
@@ -2941,12 +2957,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>7b8fec8d-6088-4881-8460-67debc4bc631</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>71c0a444-4fa7-4596-ad7d-aff132a532f1</t>
         </is>
@@ -3028,12 +3044,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>f85f4571-96c4-43b3-940f-82ed7134e305</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>50d3c8c3-5db2-4838-9100-29c974bf53d5</t>
         </is>
@@ -3115,12 +3131,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>55ebbb96-7b01-4645-8033-1d8af5273ac3</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>57a6f97d-9253-4bd8-8abf-bf5f65e82dbe</t>
         </is>
@@ -3202,12 +3218,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>5f40e82d-b270-4288-a86a-a697414005e2</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>7d47dd63-fdf0-42e6-8a27-d83a9cb2be4d</t>
         </is>
@@ -3339,20 +3355,25 @@
       </c>
       <c r="X38" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y38" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y38" s="1" t="inlineStr">
+      <c r="Z38" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z38" s="1" t="inlineStr">
+      <c r="AA38" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA38" s="1" t="inlineStr">
+      <c r="AB38" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3444,12 +3465,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>a4dbf515-b777-4149-962b-f259fe7b1d13</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>ced2dd01-336f-4ece-8a82-17beefc57fe8</t>
         </is>
@@ -3526,17 +3547,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>6345afef-efa2-4868-ac30-6ab0b5916152</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>a4aa55fd-8c7d-40a9-8cbc-ad9e70002fd6</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>a4dbf515-b777-4149-962b-f259fe7b1d13</t>
         </is>
@@ -3628,17 +3649,17 @@
           <t>hh-L</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>b28cfe0c-6ead-404a-9828-0829da27ac65</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>827190bd-c145-45d0-b13a-19a072727ffc</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>6345afef-efa2-4868-ac30-6ab0b5916152</t>
         </is>
@@ -3730,17 +3751,17 @@
           <t>hh-h</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>a67f349f-3134-4cee-9abd-76598d7536a5</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>b775fbcb-ee35-4603-98fd-eb7fd520c8b1</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>6345afef-efa2-4868-ac30-6ab0b5916152</t>
         </is>
@@ -3832,12 +3853,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>003abbef-3ced-4a35-8566-6252e853755c</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>2d7765ff-de5e-412e-b9ce-93c83ac39ae1</t>
         </is>
@@ -3929,12 +3950,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>f25a0652-0b44-41a0-8a19-dbc0d4b331e3</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>73afb3d0-2e7a-4a31-827c-34e51bfa4a7d</t>
         </is>
@@ -4031,12 +4052,12 @@
           <t>Holding down after the move will cancel recovery frames.</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>5b499286-d441-4035-b878-08da0ba8833f</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>6f654da3-b944-45c0-868c-4f5b6c46f267</t>
         </is>
@@ -4113,17 +4134,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>5e94fcc5-48fe-4496-a146-8979b18e125b</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>60d9beea-d708-40bc-ad27-19423f182ba0</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>5b499286-d441-4035-b878-08da0ba8833f</t>
         </is>
@@ -4215,17 +4236,17 @@
           <t>mxm</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>5acd76a9-889d-40f8-8573-1cde297ab24e</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>80c7c0f6-8672-4de4-8983-f9688ada8741</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>5e94fcc5-48fe-4496-a146-8979b18e125b</t>
         </is>
@@ -4287,12 +4308,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>5a2504e0-d445-49f8-ac00-40815f5d7b10</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>16169136-d6a4-4b32-861b-32cf22abf062</t>
         </is>
@@ -4394,12 +4415,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>8c19faae-5809-47e2-8e16-12098e5beca8</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>962b9b9f-cee6-4050-8402-075e3d84e599</t>
         </is>
@@ -4491,12 +4512,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>10d40578-149e-4f8d-88eb-f89af9ce2acd</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>e21abbed-9bf2-46b5-8634-9431e6155dc8</t>
         </is>
@@ -4593,12 +4614,12 @@
           <t>JGc</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>1d9fe13c-d9f4-4a8d-a7da-074ff3b00540</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>edc89fdb-8b54-4494-8d8c-812afc1cef1b</t>
         </is>
@@ -4695,12 +4716,12 @@
           <t>SH</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>7c72fb14-36ed-4ddf-b8e0-a4cdc5c86a52</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>b87f347d-d1bb-49b3-acab-bcf3a8f2a353</t>
         </is>
@@ -4797,12 +4818,12 @@
           <t>Side Stepping right away after the move will cancel recovery frames.</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>3d952a28-8768-4e62-a714-7634a3114bdf</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>5a970f0c-c60d-49e0-8813-8f6ca0a85001</t>
         </is>
@@ -4894,12 +4915,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>3e0073b4-d9d8-4093-9e59-d0d6234ac5fc</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>750500e1-a2bd-45c1-b140-10cc815398f9</t>
         </is>
@@ -4996,12 +5017,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>a9aed9ab-3213-404a-8999-db0a5080592a</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>0c43e48b-12b7-401e-82da-c96aed682342</t>
         </is>
@@ -5093,12 +5114,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>b181e799-480d-4934-bffb-e68585285059</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>d20a87f6-2a8e-46a6-ade6-fb18fd31bf7e</t>
         </is>
@@ -5195,12 +5216,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>ce601b9e-9480-4a40-b9a7-373559a41f32</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>627ccce4-3042-47a5-ad53-be1caa44f50c</t>
         </is>
@@ -5292,12 +5313,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>3c3ed592-430e-44a2-8888-6af900a9788a</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>1d33903f-f117-4798-82c9-0b12c075e7fd</t>
         </is>
@@ -5394,12 +5415,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>3398a120-61a1-4fc2-b813-34ff6ec1384c</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>2f898882-249e-4a5c-b55c-622926b29973</t>
         </is>
@@ -5496,17 +5517,17 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>27918d65-4fd7-4541-90ed-ba02908d13d6</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>c9285729-0ec2-4049-b75a-f7d5e3813190</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>3398a120-61a1-4fc2-b813-34ff6ec1384c</t>
         </is>
@@ -5588,17 +5609,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>a2b9ad8e-ceaf-4131-9908-339e455835c0</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>745c6aa8-0f35-49f3-8a11-e64d2e9e3ea7</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>27918d65-4fd7-4541-90ed-ba02908d13d6</t>
         </is>
@@ -5680,17 +5701,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>708d2132-d01f-4a05-b5ca-ea17b04d9da0</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>3116ee41-e657-4de7-a431-bf27c9bc094a</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>27918d65-4fd7-4541-90ed-ba02908d13d6</t>
         </is>
@@ -5772,17 +5793,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>f36b0997-0458-4353-a3d7-8497e6716452</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>c22ffc29-678b-4bf1-aaea-3abb89a8d03c</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>27918d65-4fd7-4541-90ed-ba02908d13d6</t>
         </is>
@@ -5874,17 +5895,17 @@
           <t>Continue with the Leg Whip Strings.</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>932c1d54-4259-488d-b0ee-aa004b63266e</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>6c31e269-b871-47f8-8f7c-cebf2cde6b66</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>3398a120-61a1-4fc2-b813-34ff6ec1384c</t>
         </is>
@@ -5971,17 +5992,17 @@
           <t>mM</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>efb55281-1c2c-4e35-984c-4c9b4b106da5</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>95951352-aea6-4e91-8a6a-7bb1b2681cfd</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>3398a120-61a1-4fc2-b813-34ff6ec1384c</t>
         </is>
@@ -6073,17 +6094,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>6352e0bb-fc5e-48ad-8941-fc1b289167aa</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>196380f5-0ff7-47d1-b317-9ab4d6bed032</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>3398a120-61a1-4fc2-b813-34ff6ec1384c</t>
         </is>
@@ -6170,17 +6191,17 @@
           <t>mLl</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>4d3ee92e-c72e-4c16-a26d-664ba55f5469</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>6852f5fc-410e-4e90-b63f-8c354f840803</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>6352e0bb-fc5e-48ad-8941-fc1b289167aa</t>
         </is>
@@ -6272,17 +6293,17 @@
           <t>Holding down after the move will cancel recovery frames.</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>d797e17f-d819-42ee-9c7c-30d7620942b0</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>ad2e942a-cbbb-4a36-a262-a3299534b5cc</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>6352e0bb-fc5e-48ad-8941-fc1b289167aa</t>
         </is>
@@ -6359,17 +6380,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>2c5ec9f2-1bab-443a-a3b6-de0f45f53246</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>5632cfe4-4379-406d-8442-b2d2059117d2</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>d797e17f-d819-42ee-9c7c-30d7620942b0</t>
         </is>
@@ -6461,17 +6482,17 @@
           <t>mLmxm</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>d4483432-49d0-49f3-9ff4-93c3764a7d38</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>d9d0d79b-14db-468c-a70a-451f72ecffcb</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>2c5ec9f2-1bab-443a-a3b6-de0f45f53246</t>
         </is>
@@ -6568,12 +6589,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>5ab8268a-215e-4f04-bf8e-a96f71ac507a</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>7bd33611-7147-4097-a59b-001aa74a054f</t>
         </is>
@@ -6670,12 +6691,12 @@
           <t>The Handstand Position will cancel the hit.</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>bec58a9f-3228-4419-babf-28b3cc3edb64</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>984c49cf-b254-45f8-baaa-7f9d093f90fc</t>
         </is>
@@ -6777,12 +6798,12 @@
           <t>KS</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>2fdf90ca-3648-460d-9ea8-a16f3d5f25e1</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>0fc7a0d5-45f1-40dd-855b-f3669869934f</t>
         </is>
@@ -6791,22 +6812,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>f,f+3+4 [~5]</t>
+          <t>f,f+3+4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>f,f+3+4 [~5]</t>
+          <t>f,f+3+4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Boomerang [Tag]</t>
+          <t>Boomerang</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Boomerang [Tag]</t>
+          <t>Boomerang</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6881,10 +6902,15 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
           <t>b389cc4c-fe71-43e2-9cca-dd7cc80d3206</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>f83a689a-731c-4ab7-8ae2-0ec838b6d8d1</t>
         </is>
@@ -6893,22 +6919,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>df+3+4 [~5]</t>
+          <t>df+3+4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>df+3+4 [~5]</t>
+          <t>df+3+4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Freak SHOW [Tag]</t>
+          <t>Freak SHOW</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Freak SHOW [Tag]</t>
+          <t>Freak SHOW</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6988,10 +7014,15 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
           <t>c15468ea-41f1-4b6a-93ab-eca6cd632675</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>ba43854c-421b-428b-a6ac-0125cfcaa463</t>
         </is>
@@ -7093,12 +7124,12 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>8304ed6b-41b5-404d-a577-c0dfb41da1c8</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>bb55fd1f-1a02-4e63-aa9d-116ef85e52af</t>
         </is>
@@ -7190,17 +7221,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>9d075145-17ed-4f3b-a39c-c29cb0995dd2</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>00a82c78-3314-4a8a-9b6a-59f3dacbb906</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>8304ed6b-41b5-404d-a577-c0dfb41da1c8</t>
         </is>
@@ -7287,17 +7318,17 @@
           <t>LLLl</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>14b1b2bb-a746-4688-af50-32c457a27e51</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>5781a6c5-0b11-4730-a644-e70604081184</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>8304ed6b-41b5-404d-a577-c0dfb41da1c8</t>
         </is>
@@ -7389,17 +7420,17 @@
           <t>Holding down after the move will cancel recovery frames.</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>b64dc694-fe0d-4485-aa80-6f416c1d29bc</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>16a05db1-8467-4384-9006-c82f2c8dc7e3</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>8304ed6b-41b5-404d-a577-c0dfb41da1c8</t>
         </is>
@@ -7476,17 +7507,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>082e994c-53e1-4a9a-9ecc-c6d0aaea6ef1</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>336d075e-be74-40d4-857b-1477130f8572</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>b64dc694-fe0d-4485-aa80-6f416c1d29bc</t>
         </is>
@@ -7573,17 +7604,17 @@
           <t>LLLmxm</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>37e55208-6568-4234-86cb-5953e0b81400</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>96c0541c-573e-4677-bd34-3c01e918893d</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>082e994c-53e1-4a9a-9ecc-c6d0aaea6ef1</t>
         </is>
@@ -7685,12 +7716,12 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>5446834c-b9b2-4c40-a6e1-fcd286309e94</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>0a2251a3-f6b0-40df-9f28-758f540707cc</t>
         </is>
@@ -7782,12 +7813,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>283019e7-1d47-45e1-ae02-1e0c20e98774</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>55035b13-b390-4e5e-be99-5d3a642b01f9</t>
         </is>
@@ -7884,12 +7915,12 @@
           <t>Links into the Slippery Kick series with either 3+4 or 3~4.</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>c26557d6-15d4-466d-8bd2-40b947e2fa28</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>bea6f9ba-b1d0-4164-bf21-6b128d509080</t>
         </is>
@@ -7946,12 +7977,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>7c6da183-2f70-4ebf-a286-aa52d565d658</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>ba8b635a-ce42-45cb-bf36-9e5090c3a60e</t>
         </is>
@@ -8043,17 +8074,17 @@
           <t>-L</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>2de6087c-1043-4135-b838-17001b8ca994</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>8fc89030-7358-48b9-9a42-c4ee6334f9f4</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>7c6da183-2f70-4ebf-a286-aa52d565d658</t>
         </is>
@@ -8145,17 +8176,17 @@
           <t>-h</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>a8c7585b-c020-45f1-8cc0-a43f4318e2ff</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>30549a46-b86e-4101-95d2-a9230d87bdc4</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>7c6da183-2f70-4ebf-a286-aa52d565d658</t>
         </is>
@@ -8247,12 +8278,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>33464d6d-9733-4687-8de9-21cf41c6913c</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>92a8137d-b6dd-4337-8471-55f58505980d</t>
         </is>
@@ -8349,12 +8380,12 @@
           <t>CSc</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>645139de-3cd1-47d1-9843-d01f8442ab39</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>28a6e850-c445-4e20-a581-ae83fef086c8</t>
         </is>
@@ -8446,17 +8477,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>e0c3444e-aae6-4eb9-9865-41b5d617f5e5</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>8b658d35-60d1-4f66-a6ee-0e411ba0711e</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>645139de-3cd1-47d1-9843-d01f8442ab39</t>
         </is>
@@ -8548,17 +8579,17 @@
           <t>hLm</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>23a5f617-c8b7-4997-a3ca-3e6128b182a1</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>750b53eb-7bd4-4027-8d53-cbc3cc8ebb2e</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>e0c3444e-aae6-4eb9-9865-41b5d617f5e5</t>
         </is>
@@ -8640,17 +8671,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>667a50db-512b-434c-8c9c-0b7ddc6df770</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>7b752f38-7dce-4a3f-a5d3-c91e0407b57c</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>23a5f617-c8b7-4997-a3ca-3e6128b182a1</t>
         </is>
@@ -8732,17 +8763,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>5b63c3b1-3eb2-42a4-a61f-f153d15df252</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>0e5264ce-0494-44a5-a86a-0e3798405fa8</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>23a5f617-c8b7-4997-a3ca-3e6128b182a1</t>
         </is>
@@ -8824,17 +8855,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>478ef843-be53-4990-b252-b0211118ec7c</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>86551c90-29fd-4de5-bff5-1f7fc0f25655</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>23a5f617-c8b7-4997-a3ca-3e6128b182a1</t>
         </is>
@@ -8926,17 +8957,17 @@
           <t>Continue with the Leg Whip Strings.</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>be01039c-a6a4-4ef1-ab05-29ec1676d5b2</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>a53245a4-dd75-4770-8e1f-e1ca222c12a3</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
+      <c r="AA95" t="inlineStr">
         <is>
           <t>e0c3444e-aae6-4eb9-9865-41b5d617f5e5</t>
         </is>
@@ -9023,17 +9054,17 @@
           <t>hLM</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>5f936ef0-957f-46ee-b7ac-e5f0ee5b2e80</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>6a8c9786-40db-478f-9208-5de3ece8bd68</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>e0c3444e-aae6-4eb9-9865-41b5d617f5e5</t>
         </is>
@@ -9125,17 +9156,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>c89588be-ef77-49f2-aa4b-f50702afd7b5</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>58b1a2be-a247-4c52-b6af-df3e794ae84f</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>e0c3444e-aae6-4eb9-9865-41b5d617f5e5</t>
         </is>
@@ -9227,17 +9258,17 @@
           <t>Holding down after the move will cancel recovery frames.</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="Y98" t="inlineStr">
         <is>
           <t>a441e5dc-3dfb-4f7e-a341-dd384961fbb1</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>2c2b2228-2aa3-48ba-8c05-cb94ab275b06</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="AA98" t="inlineStr">
         <is>
           <t>c89588be-ef77-49f2-aa4b-f50702afd7b5</t>
         </is>
@@ -9314,17 +9345,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>2616a4dd-7d4f-4ca3-91a5-191db3c7955e</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>2d16147b-7264-4b4b-8a8a-8c9e10b1840b</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>c89588be-ef77-49f2-aa4b-f50702afd7b5</t>
         </is>
@@ -9411,17 +9442,17 @@
           <t>hLL-m</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>e19a8805-c2e4-4014-b1f0-a3c971eacb73</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>f1ef94f6-ee6b-4efd-9b21-34a1a3cb409e</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>2616a4dd-7d4f-4ca3-91a5-191db3c7955e</t>
         </is>
@@ -9508,17 +9539,17 @@
           <t>hLLl</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="Y101" t="inlineStr">
         <is>
           <t>19930be2-c919-4d95-9092-ae4efe759060</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Z101" t="inlineStr">
         <is>
           <t>bee2d308-fe6b-4663-9940-6e51535a3dad</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
+      <c r="AA101" t="inlineStr">
         <is>
           <t>c89588be-ef77-49f2-aa4b-f50702afd7b5</t>
         </is>
@@ -9605,17 +9636,17 @@
           <t>hMM</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>635b15ef-4bc4-43e3-9185-c134f5ba4677</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>c524515c-d9b0-4ec2-8fc0-548afbbf347d</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
+      <c r="AA102" t="inlineStr">
         <is>
           <t>645139de-3cd1-47d1-9843-d01f8442ab39</t>
         </is>
@@ -9702,17 +9733,17 @@
           <t>hMMM</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
+      <c r="Y103" t="inlineStr">
         <is>
           <t>e164c6fa-7944-4928-8b79-ef3dd04769ea</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
+      <c r="Z103" t="inlineStr">
         <is>
           <t>3ed2cde6-5354-4001-85ef-cb7d25a91754</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
+      <c r="AA103" t="inlineStr">
         <is>
           <t>645139de-3cd1-47d1-9843-d01f8442ab39</t>
         </is>
@@ -9809,12 +9840,12 @@
           <t>Can be continued infinitely.</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>6e361000-d4f0-4731-978c-ef27d00d1a84</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>84fbd428-9800-49bd-8ba0-d56663d712bc</t>
         </is>
@@ -9911,12 +9942,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="Y105" t="inlineStr">
         <is>
           <t>8914f23d-a49e-49d4-a78b-345e8134c95a</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>a7747524-95e6-4e43-a857-96514478bfce</t>
         </is>
@@ -10008,12 +10039,12 @@
           <t>mh</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>ea4e96d7-dbbf-4189-aa7f-54bb2ba314aa</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>644152ee-8d17-421d-8487-b0b6a8e59c77</t>
         </is>
@@ -10105,17 +10136,17 @@
           <t>mhm</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr">
+      <c r="Y107" t="inlineStr">
         <is>
           <t>a70b9e10-88a1-4a3b-8a3f-6c4d62484351</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>4939c92c-6e15-4eab-8894-f14fc71d4718</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
+      <c r="AA107" t="inlineStr">
         <is>
           <t>ea4e96d7-dbbf-4189-aa7f-54bb2ba314aa</t>
         </is>
@@ -10207,12 +10238,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
+      <c r="Y108" t="inlineStr">
         <is>
           <t>b28f0455-bb63-4a5d-baa8-dd8450cf34fe</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
+      <c r="Z108" t="inlineStr">
         <is>
           <t>b10cfea2-6cca-4098-b743-3164e76ae9e2</t>
         </is>
@@ -10269,12 +10300,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
+      <c r="Y109" t="inlineStr">
         <is>
           <t>65b0f41b-9d74-45ef-aa0d-f709601122e6</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>a8bf87ae-c064-467c-81e9-46f441fb26c7</t>
         </is>
@@ -10331,12 +10362,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="Y110" t="inlineStr">
         <is>
           <t>33619bbd-ea93-4026-8169-7a0deaf141bd</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>15ffbab3-d680-435e-b17c-73d9d90e6922</t>
         </is>
@@ -10468,20 +10499,25 @@
       </c>
       <c r="X113" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y113" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y113" s="1" t="inlineStr">
+      <c r="Z113" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z113" s="1" t="inlineStr">
+      <c r="AA113" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA113" s="1" t="inlineStr">
+      <c r="AB113" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -10498,12 +10534,12 @@
           <t>Moves starting from Handstand Position only - HSP</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="Y114" t="inlineStr">
         <is>
           <t>5f6a2960-0771-413b-9f0b-e8c481e60a9f</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
+      <c r="Z114" t="inlineStr">
         <is>
           <t>be647f57-edc9-4709-bf29-e5bb34984d6e</t>
         </is>
@@ -10565,12 +10601,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
+      <c r="Y115" t="inlineStr">
         <is>
           <t>23a86858-a5af-4061-b595-c048ffa5e0ea</t>
         </is>
       </c>
-      <c r="Y115" t="inlineStr">
+      <c r="Z115" t="inlineStr">
         <is>
           <t>815fb48d-4f62-47b3-834b-bcb1f673014d</t>
         </is>
@@ -10627,12 +10663,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="Y116" t="inlineStr">
         <is>
           <t>d19752d4-1385-4f51-a7fd-b53e1a82a2d6</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
+      <c r="Z116" t="inlineStr">
         <is>
           <t>75c0556a-eea6-4411-9be7-f9d69ad86c11</t>
         </is>
@@ -10689,12 +10725,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="Y117" t="inlineStr">
         <is>
           <t>ddeb97e3-408e-431d-a376-653d303a8e74</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Z117" t="inlineStr">
         <is>
           <t>51b8771e-4dc8-4299-9d70-8b8f171a6119</t>
         </is>
@@ -10751,12 +10787,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="Y118" t="inlineStr">
         <is>
           <t>d5072ac8-5b2c-4238-af93-2be6fed6e850</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>2c4e3e13-6c58-4f15-91d8-ce7e531fc26c</t>
         </is>
@@ -10813,12 +10849,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
+      <c r="Y119" t="inlineStr">
         <is>
           <t>ea8439e5-4984-41a7-ab55-81ecc867c1cd</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="Z119" t="inlineStr">
         <is>
           <t>f73f5c3d-92a7-4c62-9805-43c4cc206747</t>
         </is>
@@ -10875,12 +10911,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="Y120" t="inlineStr">
         <is>
           <t>c2d21e2d-66e0-46d4-9733-c8f936ca3d82</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Z120" t="inlineStr">
         <is>
           <t>fc7b77a4-f1c5-4ea8-a313-46e23e625a23</t>
         </is>
@@ -10982,12 +11018,12 @@
           <t>Continue with the Leg Whip Strings.</t>
         </is>
       </c>
-      <c r="X121" t="inlineStr">
+      <c r="Y121" t="inlineStr">
         <is>
           <t>511c5803-e5cd-47d4-8b8a-4da8499f5ec6</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Z121" t="inlineStr">
         <is>
           <t>2c914bd9-7ae6-48cc-8c08-e4722a912cf2</t>
         </is>
@@ -11084,12 +11120,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
+      <c r="Y122" t="inlineStr">
         <is>
           <t>4510911a-6378-49ee-b18f-8b95ee7d73e1</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="Z122" t="inlineStr">
         <is>
           <t>4b07173b-e8f3-4dc6-824a-6b3b6476e46c</t>
         </is>
@@ -11176,17 +11212,17 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="X123" t="inlineStr">
+      <c r="Y123" t="inlineStr">
         <is>
           <t>0f5c0eb7-d105-4c6d-9baa-b93ca74ce569</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="Z123" t="inlineStr">
         <is>
           <t>a5bb7be7-ae1b-4b04-b3f5-10f712e7f767</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
+      <c r="AA123" t="inlineStr">
         <is>
           <t>4510911a-6378-49ee-b18f-8b95ee7d73e1</t>
         </is>
@@ -11273,17 +11309,17 @@
           <t>mLL</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr">
+      <c r="Y124" t="inlineStr">
         <is>
           <t>dd12a5b9-ca44-461c-8fc7-b760b2f8b012</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Z124" t="inlineStr">
         <is>
           <t>cff89a66-2d56-4cfe-9731-6b18d2c42f6b</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
+      <c r="AA124" t="inlineStr">
         <is>
           <t>0f5c0eb7-d105-4c6d-9baa-b93ca74ce569</t>
         </is>
@@ -11380,12 +11416,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
+      <c r="Y125" t="inlineStr">
         <is>
           <t>41acd87c-f316-4882-b1b7-eacda2606ad9</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="Z125" t="inlineStr">
         <is>
           <t>92c0063c-9726-4a89-97f9-3d6526295498</t>
         </is>
@@ -11482,12 +11518,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
+      <c r="Y126" t="inlineStr">
         <is>
           <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="Z126" t="inlineStr">
         <is>
           <t>cc9dd02e-62c6-4f80-b851-7431eb9b62e1</t>
         </is>
@@ -11569,17 +11605,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
+      <c r="Y127" t="inlineStr">
         <is>
           <t>5d5bb8d2-5bd6-4ba0-8501-9e44a2e15df9</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="Z127" t="inlineStr">
         <is>
           <t>b24c516d-9014-4da2-b916-2a8e8acf8910</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
+      <c r="AA127" t="inlineStr">
         <is>
           <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
         </is>
@@ -11661,17 +11697,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X128" t="inlineStr">
+      <c r="Y128" t="inlineStr">
         <is>
           <t>65079a7b-bb56-4efa-9b40-c8f270a11cd4</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="Z128" t="inlineStr">
         <is>
           <t>03a0d7ad-1c8a-4e35-81b5-d05d1bdc8882</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
+      <c r="AA128" t="inlineStr">
         <is>
           <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
         </is>
@@ -11753,17 +11789,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X129" t="inlineStr">
+      <c r="Y129" t="inlineStr">
         <is>
           <t>5198b605-f40c-4dce-9eb1-1157941a6432</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
+      <c r="Z129" t="inlineStr">
         <is>
           <t>caa0e393-e3a3-42f8-b7cf-544f57c555f1</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
+      <c r="AA129" t="inlineStr">
         <is>
           <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
         </is>
@@ -11860,12 +11896,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
+      <c r="Y130" t="inlineStr">
         <is>
           <t>2eb8116e-8d2f-41a0-8e3d-fca4561f091c</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
+      <c r="Z130" t="inlineStr">
         <is>
           <t>70e07ec3-352b-4cce-8d3b-7e16566602b9</t>
         </is>
@@ -11967,12 +12003,12 @@
           <t>M</t>
         </is>
       </c>
-      <c r="X131" t="inlineStr">
+      <c r="Y131" t="inlineStr">
         <is>
           <t>7f64d48a-61da-46a7-a8de-d8f58b8776a8</t>
         </is>
       </c>
-      <c r="Y131" t="inlineStr">
+      <c r="Z131" t="inlineStr">
         <is>
           <t>ab5704d1-37fb-4bf8-9616-a41a6a9d73a0</t>
         </is>
@@ -12074,12 +12110,12 @@
           <t>Continue with the Slippery Kick Series.</t>
         </is>
       </c>
-      <c r="X132" t="inlineStr">
+      <c r="Y132" t="inlineStr">
         <is>
           <t>bffcbff7-db7d-4043-ac47-9ee47ec87cc6</t>
         </is>
       </c>
-      <c r="Y132" t="inlineStr">
+      <c r="Z132" t="inlineStr">
         <is>
           <t>29558096-0108-4b85-8165-a9e0295a1d84</t>
         </is>
@@ -12088,22 +12124,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>d+3+4 [~5]</t>
+          <t>d+3+4</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>d+3+4 [~5]</t>
+          <t>d+3+4</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Perch Flop Kick [Tag]</t>
+          <t>Perch Flop Kick</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Perch Flop Kick [Tag]</t>
+          <t>Perch Flop Kick</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -12183,10 +12219,15 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
           <t>8b720acf-7ec6-4577-893b-bfb5d6cb43e3</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
+      <c r="Z133" t="inlineStr">
         <is>
           <t>eadfcd53-259d-4c25-aed7-e4fe2240079b</t>
         </is>
@@ -12283,12 +12324,12 @@
           <t>sh</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr">
+      <c r="Y134" t="inlineStr">
         <is>
           <t>8acded53-2f9d-4323-bcaf-0766f532f837</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
+      <c r="Z134" t="inlineStr">
         <is>
           <t>70d2decc-0404-46a5-9bd6-ce9e83a292e8</t>
         </is>
@@ -12420,20 +12461,25 @@
       </c>
       <c r="X137" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y137" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y137" s="1" t="inlineStr">
+      <c r="Z137" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z137" s="1" t="inlineStr">
+      <c r="AA137" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA137" s="1" t="inlineStr">
+      <c r="AB137" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -12450,12 +12496,12 @@
           <t>Moves starting from Rewinder only - SS_1+2_d+1+2</t>
         </is>
       </c>
-      <c r="X138" t="inlineStr">
+      <c r="Y138" t="inlineStr">
         <is>
           <t>1969a61d-d20b-4b1b-8033-5be235b5db5e</t>
         </is>
       </c>
-      <c r="Y138" t="inlineStr">
+      <c r="Z138" t="inlineStr">
         <is>
           <t>797c1da6-3b7a-4181-ba6c-f97f1dda8d7a</t>
         </is>
@@ -12552,12 +12598,12 @@
           <t>Side Stepping right away after the move will cancel recovery frames.</t>
         </is>
       </c>
-      <c r="X139" t="inlineStr">
+      <c r="Y139" t="inlineStr">
         <is>
           <t>56ee9908-67b8-4b86-acec-e94fdc61ccbd</t>
         </is>
       </c>
-      <c r="Y139" t="inlineStr">
+      <c r="Z139" t="inlineStr">
         <is>
           <t>fb2443ea-f19d-4232-9488-401e0da62004</t>
         </is>
@@ -12566,22 +12612,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>– ~3 [~5]</t>
+          <t>– ~3</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1+2~3 [~5]</t>
+          <t>1+2~3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>– Freak SHOW [Tag]</t>
+          <t>– Freak SHOW</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Spin Slaps – Freak SHOW [Tag]</t>
+          <t>Spin Slaps – Freak SHOW</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -12636,15 +12682,20 @@
       </c>
       <c r="X140" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
           <t>decc1aa4-e980-405e-a16f-97860935c01f</t>
         </is>
       </c>
-      <c r="Y140" t="inlineStr">
+      <c r="Z140" t="inlineStr">
         <is>
           <t>77eb6285-7418-4ba7-ab4f-19d0021b8943</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
+      <c r="AA140" t="inlineStr">
         <is>
           <t>56ee9908-67b8-4b86-acec-e94fdc61ccbd</t>
         </is>
@@ -12736,17 +12787,17 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X141" t="inlineStr">
+      <c r="Y141" t="inlineStr">
         <is>
           <t>86e0c0eb-7179-4183-92d4-4e8d042753f2</t>
         </is>
       </c>
-      <c r="Y141" t="inlineStr">
+      <c r="Z141" t="inlineStr">
         <is>
           <t>5fd587ac-ad54-416d-bd30-29dd088a5f08</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
+      <c r="AA141" t="inlineStr">
         <is>
           <t>56ee9908-67b8-4b86-acec-e94fdc61ccbd</t>
         </is>
@@ -12838,12 +12889,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X142" t="inlineStr">
+      <c r="Y142" t="inlineStr">
         <is>
           <t>e538d91b-84e9-428e-90f0-cfddcc451c34</t>
         </is>
       </c>
-      <c r="Y142" t="inlineStr">
+      <c r="Z142" t="inlineStr">
         <is>
           <t>24156857-1b0c-44c2-972e-48a8863b6b0d</t>
         </is>
@@ -12900,12 +12951,12 @@
           <t>BNc GB</t>
         </is>
       </c>
-      <c r="X143" t="inlineStr">
+      <c r="Y143" t="inlineStr">
         <is>
           <t>b90f4753-8d6d-4a51-9de4-15e59430ea1c</t>
         </is>
       </c>
-      <c r="Y143" t="inlineStr">
+      <c r="Z143" t="inlineStr">
         <is>
           <t>a61fd67a-7ccf-44a9-a03e-58f997dd8ba5</t>
         </is>
@@ -13002,12 +13053,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X144" t="inlineStr">
+      <c r="Y144" t="inlineStr">
         <is>
           <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
         </is>
       </c>
-      <c r="Y144" t="inlineStr">
+      <c r="Z144" t="inlineStr">
         <is>
           <t>7ce85b52-35c9-48f7-86de-f6d0cbd8c772</t>
         </is>
@@ -13089,17 +13140,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X145" t="inlineStr">
+      <c r="Y145" t="inlineStr">
         <is>
           <t>466a2f97-19a0-4c71-a160-d54dee120154</t>
         </is>
       </c>
-      <c r="Y145" t="inlineStr">
+      <c r="Z145" t="inlineStr">
         <is>
           <t>40c9a433-8ac2-46c7-be6f-f7d1c270a106</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
+      <c r="AA145" t="inlineStr">
         <is>
           <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
         </is>
@@ -13181,17 +13232,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X146" t="inlineStr">
+      <c r="Y146" t="inlineStr">
         <is>
           <t>0b29efa5-c707-407b-8c14-df015fa1a042</t>
         </is>
       </c>
-      <c r="Y146" t="inlineStr">
+      <c r="Z146" t="inlineStr">
         <is>
           <t>14c72d8f-e908-4034-85ed-0df40c791668</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
+      <c r="AA146" t="inlineStr">
         <is>
           <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
         </is>
@@ -13273,17 +13324,17 @@
           <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
-      <c r="X147" t="inlineStr">
+      <c r="Y147" t="inlineStr">
         <is>
           <t>b8a0c0e0-a2b7-44a5-ab85-7f94be747875</t>
         </is>
       </c>
-      <c r="Y147" t="inlineStr">
+      <c r="Z147" t="inlineStr">
         <is>
           <t>da7e3889-2bfa-4965-9152-a5515386e0b9</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
+      <c r="AA147" t="inlineStr">
         <is>
           <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
         </is>
@@ -13292,22 +13343,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>–– 3+4 [~5]</t>
+          <t>–– 3+4</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3,B,3+4 [~5]</t>
+          <t>3,B,3+4</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>–– Instant Perch Flop Kick [Tag]</t>
+          <t>–– Instant Perch Flop Kick</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Hot Plate – Handstand Position – Instant Perch Flop Kick [Tag]</t>
+          <t>Hot Plate – Handstand Position – Instant Perch Flop Kick</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -13387,15 +13438,20 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
           <t>3d796a62-d26d-4bf4-834d-dc8d84196084</t>
         </is>
       </c>
-      <c r="Y148" t="inlineStr">
+      <c r="Z148" t="inlineStr">
         <is>
           <t>922b1b94-f5ed-46d6-9b82-351305cbf0e9</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
+      <c r="AA148" t="inlineStr">
         <is>
           <t>b8a0c0e0-a2b7-44a5-ab85-7f94be747875</t>
         </is>
@@ -13487,12 +13543,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X149" t="inlineStr">
+      <c r="Y149" t="inlineStr">
         <is>
           <t>afb81e0e-130a-49a0-94b7-44302f09074e</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
+      <c r="Z149" t="inlineStr">
         <is>
           <t>9cc5b23d-9118-44f6-bb48-2b737d8e2ccb</t>
         </is>
@@ -13584,17 +13640,17 @@
           <t>BN GB</t>
         </is>
       </c>
-      <c r="X150" t="inlineStr">
+      <c r="Y150" t="inlineStr">
         <is>
           <t>87d9fba7-d027-4cb2-b63b-2d9f533af40d</t>
         </is>
       </c>
-      <c r="Y150" t="inlineStr">
+      <c r="Z150" t="inlineStr">
         <is>
           <t>336b6709-4ed8-47ad-be96-8bdc8b170076</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
+      <c r="AA150" t="inlineStr">
         <is>
           <t>afb81e0e-130a-49a0-94b7-44302f09074e</t>
         </is>
@@ -13681,17 +13737,17 @@
           <t>hmMM</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
+      <c r="Y151" t="inlineStr">
         <is>
           <t>88c0fefa-6a80-4d6b-bfe2-40aeb13f31ef</t>
         </is>
       </c>
-      <c r="Y151" t="inlineStr">
+      <c r="Z151" t="inlineStr">
         <is>
           <t>f55b7113-123a-421f-a80a-c5c581ff72c1</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
+      <c r="AA151" t="inlineStr">
         <is>
           <t>87d9fba7-d027-4cb2-b63b-2d9f533af40d</t>
         </is>
@@ -13778,17 +13834,17 @@
           <t>hmMMm</t>
         </is>
       </c>
-      <c r="X152" t="inlineStr">
+      <c r="Y152" t="inlineStr">
         <is>
           <t>49e65892-9b94-4709-9f04-ee9f63cf6a53</t>
         </is>
       </c>
-      <c r="Y152" t="inlineStr">
+      <c r="Z152" t="inlineStr">
         <is>
           <t>3b2d9faf-bb6d-467d-bf91-a07d4dfaa390</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
+      <c r="AA152" t="inlineStr">
         <is>
           <t>88c0fefa-6a80-4d6b-bfe2-40aeb13f31ef</t>
         </is>
@@ -13885,12 +13941,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X153" t="inlineStr">
+      <c r="Y153" t="inlineStr">
         <is>
           <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
         </is>
       </c>
-      <c r="Y153" t="inlineStr">
+      <c r="Z153" t="inlineStr">
         <is>
           <t>1be22aee-cacf-4c5a-990b-1ac7955f4750</t>
         </is>
@@ -13977,17 +14033,17 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X154" t="inlineStr">
+      <c r="Y154" t="inlineStr">
         <is>
           <t>259c2d7b-bde2-4a54-a2c8-a2652d2bdcfc</t>
         </is>
       </c>
-      <c r="Y154" t="inlineStr">
+      <c r="Z154" t="inlineStr">
         <is>
           <t>d0eb9d0e-6194-4d1d-a978-a68f28bbd4b4</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
+      <c r="AA154" t="inlineStr">
         <is>
           <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
         </is>
@@ -14074,17 +14130,17 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="X155" t="inlineStr">
+      <c r="Y155" t="inlineStr">
         <is>
           <t>45d6dfb2-ead1-41b0-9302-490de575aa07</t>
         </is>
       </c>
-      <c r="Y155" t="inlineStr">
+      <c r="Z155" t="inlineStr">
         <is>
           <t>e9d07751-7132-4c55-9bf7-8992825cd956</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
+      <c r="AA155" t="inlineStr">
         <is>
           <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
         </is>
@@ -14176,17 +14232,17 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="X156" t="inlineStr">
+      <c r="Y156" t="inlineStr">
         <is>
           <t>b5ed55d8-b877-4585-81ed-04d0c54660d0</t>
         </is>
       </c>
-      <c r="Y156" t="inlineStr">
+      <c r="Z156" t="inlineStr">
         <is>
           <t>bd63768b-2841-49df-9c73-59ce25b1f5dd</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
+      <c r="AA156" t="inlineStr">
         <is>
           <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
         </is>
@@ -14283,12 +14339,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X157" t="inlineStr">
+      <c r="Y157" t="inlineStr">
         <is>
           <t>9b85822a-6998-47d6-99b9-a7948eda5324</t>
         </is>
       </c>
-      <c r="Y157" t="inlineStr">
+      <c r="Z157" t="inlineStr">
         <is>
           <t>a9c85d46-aa8c-45c7-9d7b-23f81a08b889</t>
         </is>
@@ -14380,12 +14436,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X158" t="inlineStr">
+      <c r="Y158" t="inlineStr">
         <is>
           <t>da4ad8a1-db1f-4376-8397-632562b526f3</t>
         </is>
       </c>
-      <c r="Y158" t="inlineStr">
+      <c r="Z158" t="inlineStr">
         <is>
           <t>4fd67296-1b5c-4c61-a4ed-27ae40c47bcc</t>
         </is>
@@ -14472,17 +14528,17 @@
           <t>LL</t>
         </is>
       </c>
-      <c r="X159" t="inlineStr">
+      <c r="Y159" t="inlineStr">
         <is>
           <t>0f949d8c-dfc3-4c69-b3cb-55ff2a5828bf</t>
         </is>
       </c>
-      <c r="Y159" t="inlineStr">
+      <c r="Z159" t="inlineStr">
         <is>
           <t>5d52d217-0c75-48d4-bbf6-5bf0b4c61027</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
+      <c r="AA159" t="inlineStr">
         <is>
           <t>da4ad8a1-db1f-4376-8397-632562b526f3</t>
         </is>
@@ -14569,17 +14625,17 @@
           <t>LM</t>
         </is>
       </c>
-      <c r="X160" t="inlineStr">
+      <c r="Y160" t="inlineStr">
         <is>
           <t>7b616e47-8ebb-4154-8160-9d5418a3b56c</t>
         </is>
       </c>
-      <c r="Y160" t="inlineStr">
+      <c r="Z160" t="inlineStr">
         <is>
           <t>814baccb-ac03-4f45-9007-4ff47eb17944</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
+      <c r="AA160" t="inlineStr">
         <is>
           <t>da4ad8a1-db1f-4376-8397-632562b526f3</t>
         </is>
@@ -14711,20 +14767,25 @@
       </c>
       <c r="X163" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y163" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y163" s="1" t="inlineStr">
+      <c r="Z163" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z163" s="1" t="inlineStr">
+      <c r="AA163" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA163" s="1" t="inlineStr">
+      <c r="AB163" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -14741,12 +14802,12 @@
           <t>Moves starting from Relaxed Position only - RLX</t>
         </is>
       </c>
-      <c r="X164" t="inlineStr">
+      <c r="Y164" t="inlineStr">
         <is>
           <t>fbcf3956-a19f-4979-936b-a082e5c54be6</t>
         </is>
       </c>
-      <c r="Y164" t="inlineStr">
+      <c r="Z164" t="inlineStr">
         <is>
           <t>97900bc5-829d-43ca-9962-479ab0e001dc</t>
         </is>
@@ -14843,12 +14904,12 @@
           <t>Hold down or Side Step right away after the move to cancel recovery frames.</t>
         </is>
       </c>
-      <c r="X165" t="inlineStr">
+      <c r="Y165" t="inlineStr">
         <is>
           <t>522a8f03-06bd-4536-8ac7-bcec87bd1df5</t>
         </is>
       </c>
-      <c r="Y165" t="inlineStr">
+      <c r="Z165" t="inlineStr">
         <is>
           <t>0ea6d596-a148-4ec9-814c-17245b2391c3</t>
         </is>
@@ -14925,17 +14986,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X166" t="inlineStr">
+      <c r="Y166" t="inlineStr">
         <is>
           <t>5302c69a-79a4-46d9-aeee-219261a791dc</t>
         </is>
       </c>
-      <c r="Y166" t="inlineStr">
+      <c r="Z166" t="inlineStr">
         <is>
           <t>c17ad315-8dc2-44b1-a817-f968c975e092</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
+      <c r="AA166" t="inlineStr">
         <is>
           <t>522a8f03-06bd-4536-8ac7-bcec87bd1df5</t>
         </is>
@@ -15027,17 +15088,17 @@
           <t>mxm</t>
         </is>
       </c>
-      <c r="X167" t="inlineStr">
+      <c r="Y167" t="inlineStr">
         <is>
           <t>bb840600-1410-4ca3-b5b2-177cdb175063</t>
         </is>
       </c>
-      <c r="Y167" t="inlineStr">
+      <c r="Z167" t="inlineStr">
         <is>
           <t>d170efb9-e72e-472e-b3ec-5e9647abe966</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
+      <c r="AA167" t="inlineStr">
         <is>
           <t>5302c69a-79a4-46d9-aeee-219261a791dc</t>
         </is>
@@ -15089,12 +15150,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X168" t="inlineStr">
+      <c r="Y168" t="inlineStr">
         <is>
           <t>0afa8b57-c544-4c65-afdb-d72135898321</t>
         </is>
       </c>
-      <c r="Y168" t="inlineStr">
+      <c r="Z168" t="inlineStr">
         <is>
           <t>4b5b30d6-65e1-4ad9-bce2-9ad97e1ca94f</t>
         </is>
@@ -15186,12 +15247,12 @@
           <t>lm</t>
         </is>
       </c>
-      <c r="X169" t="inlineStr">
+      <c r="Y169" t="inlineStr">
         <is>
           <t>642df474-82e5-4e7a-b4bd-6a7d748319e6</t>
         </is>
       </c>
-      <c r="Y169" t="inlineStr">
+      <c r="Z169" t="inlineStr">
         <is>
           <t>de9e18f3-b06f-4501-a9dd-5e39076b810c</t>
         </is>
@@ -15288,12 +15349,12 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X170" t="inlineStr">
+      <c r="Y170" t="inlineStr">
         <is>
           <t>0d01b647-fe54-4386-8366-bf540afebbdc</t>
         </is>
       </c>
-      <c r="Y170" t="inlineStr">
+      <c r="Z170" t="inlineStr">
         <is>
           <t>f53dd120-3244-430d-8e35-b1d63c126dd1</t>
         </is>
@@ -15390,12 +15451,12 @@
           <t>Holding back will cancel the Handspring, tapping 3 will cause the Handspring to hit before going into Handstand Position.</t>
         </is>
       </c>
-      <c r="X171" t="inlineStr">
+      <c r="Y171" t="inlineStr">
         <is>
           <t>1f33d2bc-9841-4057-9510-bae5bf5e46f4</t>
         </is>
       </c>
-      <c r="Y171" t="inlineStr">
+      <c r="Z171" t="inlineStr">
         <is>
           <t>60efbe64-fb4d-4a96-906d-1bd1b8484c71</t>
         </is>
@@ -15452,12 +15513,12 @@
           <t>BT</t>
         </is>
       </c>
-      <c r="X172" t="inlineStr">
+      <c r="Y172" t="inlineStr">
         <is>
           <t>de459dcb-e7b1-47ef-ba27-674d511033cf</t>
         </is>
       </c>
-      <c r="Y172" t="inlineStr">
+      <c r="Z172" t="inlineStr">
         <is>
           <t>1d7286d3-d630-4ef5-abf7-566999d50a64</t>
         </is>
@@ -15554,12 +15615,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X173" t="inlineStr">
+      <c r="Y173" t="inlineStr">
         <is>
           <t>82fe2211-8a53-4732-be5e-580a5ee95203</t>
         </is>
       </c>
-      <c r="Y173" t="inlineStr">
+      <c r="Z173" t="inlineStr">
         <is>
           <t>27cd3819-c33c-4346-889e-0ab9113afe11</t>
         </is>
@@ -15656,12 +15717,12 @@
           <t>Hold down or Side Step right away after the move to cancel recovery frames.</t>
         </is>
       </c>
-      <c r="X174" t="inlineStr">
+      <c r="Y174" t="inlineStr">
         <is>
           <t>3f5cac11-0d1d-42c1-a09e-34f6a66ecdcf</t>
         </is>
       </c>
-      <c r="Y174" t="inlineStr">
+      <c r="Z174" t="inlineStr">
         <is>
           <t>78d3dd69-5c28-4ca9-bfaa-ffa8bd44c236</t>
         </is>
@@ -15713,12 +15774,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X175" t="inlineStr">
+      <c r="Y175" t="inlineStr">
         <is>
           <t>b76844b7-d6c4-487a-b222-0b12c1bc45ff</t>
         </is>
       </c>
-      <c r="Y175" t="inlineStr">
+      <c r="Z175" t="inlineStr">
         <is>
           <t>e8c50903-ff49-47a3-89c2-6b3321ff8098</t>
         </is>
@@ -15850,20 +15911,25 @@
       </c>
       <c r="X178" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y178" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y178" s="1" t="inlineStr">
+      <c r="Z178" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z178" s="1" t="inlineStr">
+      <c r="AA178" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA178" s="1" t="inlineStr">
+      <c r="AB178" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -15945,12 +16011,12 @@
           <t>[!][!]</t>
         </is>
       </c>
-      <c r="X179" t="inlineStr">
+      <c r="Y179" t="inlineStr">
         <is>
           <t>7adca466-0143-4227-a025-7ff5c051c8d5</t>
         </is>
       </c>
-      <c r="Y179" t="inlineStr">
+      <c r="Z179" t="inlineStr">
         <is>
           <t>71b7b8ab-5b9f-4a94-8b1c-1414b2989d18</t>
         </is>
@@ -16017,17 +16083,17 @@
           <t>[!][!]-</t>
         </is>
       </c>
-      <c r="X180" t="inlineStr">
+      <c r="Y180" t="inlineStr">
         <is>
           <t>b3b28c08-1083-41c2-acc3-3cb19e02c822</t>
         </is>
       </c>
-      <c r="Y180" t="inlineStr">
+      <c r="Z180" t="inlineStr">
         <is>
           <t>be655c1e-6671-4778-8c89-b4a0230bab93</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
+      <c r="AA180" t="inlineStr">
         <is>
           <t>7adca466-0143-4227-a025-7ff5c051c8d5</t>
         </is>
@@ -16159,20 +16225,25 @@
       </c>
       <c r="X183" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y183" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y183" s="1" t="inlineStr">
+      <c r="Z183" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z183" s="1" t="inlineStr">
+      <c r="AA183" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA183" s="1" t="inlineStr">
+      <c r="AB183" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -16214,12 +16285,12 @@
           <t>mmmhhmmmhmmm</t>
         </is>
       </c>
-      <c r="Y184" t="inlineStr">
+      <c r="Z184" t="inlineStr">
         <is>
           <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
         </is>
       </c>
-      <c r="AA184" t="inlineStr">
+      <c r="AB184" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -16261,12 +16332,12 @@
           <t>mmmhhL</t>
         </is>
       </c>
-      <c r="Y185" t="inlineStr">
+      <c r="Z185" t="inlineStr">
         <is>
           <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
         </is>
       </c>
-      <c r="AA185" t="inlineStr">
+      <c r="AB185" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -16293,17 +16364,17 @@
           <t>mmmhhL</t>
         </is>
       </c>
-      <c r="Y186" t="inlineStr">
+      <c r="Z186" t="inlineStr">
         <is>
           <t>b321b883-5528-4383-9e3a-01d93e60f6ab</t>
         </is>
       </c>
-      <c r="Z186" t="inlineStr">
+      <c r="AA186" t="inlineStr">
         <is>
           <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
         </is>
       </c>
-      <c r="AA186" t="inlineStr">
+      <c r="AB186" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/eddy_step7.xlsx
+++ b/sources/eddy_step7.xlsx
@@ -856,6 +856,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
@@ -918,6 +923,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
@@ -978,6 +988,11 @@
       <c r="U8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>89b9a62a-0e17-41f7-9bcd-95c83f81b48a</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -16885,6 +16900,11 @@
           <t>mmmhhmmmhmmm</t>
         </is>
       </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
+        </is>
+      </c>
       <c r="Z189" t="inlineStr">
         <is>
           <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
@@ -16932,6 +16952,11 @@
           <t>mmmhhL</t>
         </is>
       </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
+        </is>
+      </c>
       <c r="Z190" t="inlineStr">
         <is>
           <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
@@ -16962,6 +16987,11 @@
       <c r="S191" t="inlineStr">
         <is>
           <t>mmmhhL</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>b321b883-5528-4383-9e3a-01d93e60f6ab</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
